--- a/examples/subsets/LargeDrugCombo/raw_data/manifest.xlsx
+++ b/examples/subsets/LargeDrugCombo/raw_data/manifest.xlsx
@@ -32,7 +32,7 @@
     <t xml:space="preserve">E77903mtx17</t>
   </si>
   <si>
-    <t xml:space="preserve">template.xlsx</t>
+    <t xml:space="preserve">P41.Belva.mtx17.template.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">CL00131</t>
